--- a/data/sample.xlsx
+++ b/data/sample.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10908"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10628"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/shiho/Script/Web/chronicliner/data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/shiho/Script/chronicliner/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D3E4F34-0F78-EB4C-B0BD-4848E6670B68}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B38DC76-48B4-1946-8888-AC6C364BFAD9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14360" yWindow="5380" windowWidth="27900" windowHeight="16940" activeTab="4" xr2:uid="{D125DCEA-AF8F-4C46-AD2C-B6390BEF02A8}"/>
+    <workbookView xWindow="14360" yWindow="5380" windowWidth="27900" windowHeight="16940" activeTab="3" xr2:uid="{D125DCEA-AF8F-4C46-AD2C-B6390BEF02A8}"/>
   </bookViews>
   <sheets>
     <sheet name="カテゴリー" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="630" uniqueCount="226">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="632" uniqueCount="228">
   <si>
     <t>カテゴリ</t>
     <phoneticPr fontId="1"/>
@@ -910,6 +910,17 @@
     <t>寮フラグ回収</t>
     <rPh sb="0" eb="1">
       <t xml:space="preserve">リョウ </t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>デバッグ用</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>存在しないカテゴリ</t>
+    <rPh sb="0" eb="2">
+      <t xml:space="preserve">ソンザイシナイ </t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -938,7 +949,7 @@
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Hiragino Kaku Gothic ProN"/>
-      <charset val="128"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="12"/>
@@ -2134,7 +2145,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9B56DC81-C77C-8C49-8450-138C04F745AF}">
-  <dimension ref="A1:I147"/>
+  <dimension ref="A1:I148"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20"/>
   <cols>
     <col min="3" max="3" width="16.7109375" bestFit="1" customWidth="1"/>
@@ -4863,6 +4874,17 @@
       </c>
       <c r="I147" t="s">
         <v>224</v>
+      </c>
+    </row>
+    <row r="148" spans="1:9">
+      <c r="A148" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="B148" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="C148" s="1">
+        <v>33971</v>
       </c>
     </row>
   </sheetData>
